--- a/artfynd/A 63685-2025 artfynd.xlsx
+++ b/artfynd/A 63685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,7 +678,7 @@
         <v>132695303</v>
       </c>
       <c r="B2" t="n">
-        <v>91867</v>
+        <v>91871</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132694391</v>
       </c>
       <c r="B3" t="n">
-        <v>99112</v>
+        <v>99116</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -881,7 +881,7 @@
         <v>132694155</v>
       </c>
       <c r="B4" t="n">
-        <v>58110</v>
+        <v>58114</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -990,7 +990,7 @@
         <v>132695248</v>
       </c>
       <c r="B5" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1097,10 +1097,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132695219</v>
+        <v>132695144</v>
       </c>
       <c r="B6" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1140,10 +1140,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757221</v>
+        <v>757130</v>
       </c>
       <c r="R6" t="n">
-        <v>7175916</v>
+        <v>7175755</v>
       </c>
       <c r="S6" t="n">
         <v>5</v>
@@ -1207,10 +1207,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132695144</v>
+        <v>132695219</v>
       </c>
       <c r="B7" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1250,10 +1250,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757130</v>
+        <v>757221</v>
       </c>
       <c r="R7" t="n">
-        <v>7175755</v>
+        <v>7175916</v>
       </c>
       <c r="S7" t="n">
         <v>5</v>
@@ -1320,7 +1320,7 @@
         <v>132694004</v>
       </c>
       <c r="B8" t="n">
-        <v>79323</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1421,7 +1421,7 @@
         <v>132694051</v>
       </c>
       <c r="B9" t="n">
-        <v>79323</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>132695275</v>
       </c>
       <c r="B10" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1636,7 +1636,7 @@
         <v>132695182</v>
       </c>
       <c r="B11" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1741,7 +1741,7 @@
         <v>132694107</v>
       </c>
       <c r="B12" t="n">
-        <v>57949</v>
+        <v>57953</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1845,6 +1845,2790 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>132710001</v>
+      </c>
+      <c r="B13" t="n">
+        <v>91871</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>757256</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7175937</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>132709549</v>
+      </c>
+      <c r="B14" t="n">
+        <v>91908</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr"/>
+      <c r="N14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>756997</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7175735</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>132709496</v>
+      </c>
+      <c r="B15" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>756999</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7175722</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>132709437</v>
+      </c>
+      <c r="B16" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr"/>
+      <c r="N16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>757012</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7175727</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF16" t="inlineStr"/>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>132709455</v>
+      </c>
+      <c r="B17" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>757005</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7175716</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>132709325</v>
+      </c>
+      <c r="B18" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>757037</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7175709</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>132709608</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>757019</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7175747</v>
+      </c>
+      <c r="S19" t="n">
+        <v>10</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>132709716</v>
+      </c>
+      <c r="B20" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>757180</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7175845</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>132709430</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>757039</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7175739</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>äldre hack i basen på en jättegran</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>132709648</v>
+      </c>
+      <c r="B22" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>757096</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7175748</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>132709778</v>
+      </c>
+      <c r="B23" t="n">
+        <v>80461</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>6462</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Stuplav</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Nephroma bellum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr"/>
+      <c r="N23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>757164</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7175781</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>132709987</v>
+      </c>
+      <c r="B24" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr"/>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>757221</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7175915</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>132709870</v>
+      </c>
+      <c r="B25" t="n">
+        <v>57950</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>757170</v>
+      </c>
+      <c r="R25" t="n">
+        <v>7175864</v>
+      </c>
+      <c r="S25" t="n">
+        <v>10</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>132710019</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr"/>
+      <c r="N26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>757281</v>
+      </c>
+      <c r="R26" t="n">
+        <v>7175939</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF26" t="inlineStr"/>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>132709773</v>
+      </c>
+      <c r="B27" t="n">
+        <v>80467</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>6463</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bårdlav</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Nephroma parile</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>757164</v>
+      </c>
+      <c r="R27" t="n">
+        <v>7175781</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>132709670</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99116</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr"/>
+      <c r="N28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>757108</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7175764</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>132709941</v>
+      </c>
+      <c r="B29" t="n">
+        <v>91908</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
+      <c r="N29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>757173</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7175914</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>132709927</v>
+      </c>
+      <c r="B30" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
+      <c r="N30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>757148</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7175922</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>132708855</v>
+      </c>
+      <c r="B31" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
+      <c r="N31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>757076</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7175730</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>132709519</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
+      <c r="N32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>757001</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7175733</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF32" t="inlineStr"/>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>132709623</v>
+      </c>
+      <c r="B33" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
+      <c r="N33" t="inlineStr"/>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>757014</v>
+      </c>
+      <c r="R33" t="n">
+        <v>7175761</v>
+      </c>
+      <c r="S33" t="n">
+        <v>10</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>rik förekomst!</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF33" t="inlineStr"/>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>132709599</v>
+      </c>
+      <c r="B34" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr"/>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>757009</v>
+      </c>
+      <c r="R34" t="n">
+        <v>7175741</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF34" t="inlineStr"/>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>132709451</v>
+      </c>
+      <c r="B35" t="n">
+        <v>80432</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr"/>
+      <c r="N35" t="inlineStr"/>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>757005</v>
+      </c>
+      <c r="R35" t="n">
+        <v>7175716</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF35" t="inlineStr"/>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>132708867</v>
+      </c>
+      <c r="B36" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr"/>
+      <c r="N36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>757057</v>
+      </c>
+      <c r="R36" t="n">
+        <v>7175737</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF36" t="inlineStr"/>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>132709906</v>
+      </c>
+      <c r="B37" t="n">
+        <v>57953</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr"/>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>757157</v>
+      </c>
+      <c r="R37" t="n">
+        <v>7175889</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>1</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>132709425</v>
+      </c>
+      <c r="B38" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr"/>
+      <c r="N38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Mörttjärnliden, Vb</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>757039</v>
+      </c>
+      <c r="R38" t="n">
+        <v>7175739</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Skellefteå</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Burträsk</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Patrik Nygren</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 63685-2025 artfynd.xlsx
+++ b/artfynd/A 63685-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>132695303</v>
       </c>
       <c r="B2" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -779,7 +779,7 @@
         <v>132694391</v>
       </c>
       <c r="B3" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1851,7 +1851,7 @@
         <v>132710001</v>
       </c>
       <c r="B13" t="n">
-        <v>91871</v>
+        <v>91872</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1956,7 +1956,7 @@
         <v>132709549</v>
       </c>
       <c r="B14" t="n">
-        <v>91908</v>
+        <v>91909</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2061,7 +2061,7 @@
         <v>132709496</v>
       </c>
       <c r="B15" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2814,42 +2814,41 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132709648</v>
+        <v>132709778</v>
       </c>
       <c r="B22" t="n">
-        <v>57953</v>
+        <v>80461</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2857,10 +2856,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>757096</v>
+        <v>757164</v>
       </c>
       <c r="R22" t="n">
-        <v>7175748</v>
+        <v>7175781</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2895,17 +2894,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
       <c r="AE22" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF22" t="inlineStr"/>
       <c r="AG22" t="b">
         <v>0</v>
       </c>
@@ -2924,41 +2919,42 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132709778</v>
+        <v>132709648</v>
       </c>
       <c r="B23" t="n">
-        <v>80461</v>
+        <v>57953</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2966,10 +2962,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>757164</v>
+        <v>757096</v>
       </c>
       <c r="R23" t="n">
-        <v>7175781</v>
+        <v>7175748</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3004,13 +3000,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF23" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3136,42 +3136,42 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132709870</v>
+        <v>132710019</v>
       </c>
       <c r="B25" t="n">
-        <v>57950</v>
+        <v>99117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3179,10 +3179,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>757170</v>
+        <v>757281</v>
       </c>
       <c r="R25" t="n">
-        <v>7175864</v>
+        <v>7175939</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3217,17 +3217,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>hål hackat i gran</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
       <c r="AE25" t="b">
         <v>0</v>
       </c>
+      <c r="AF25" t="inlineStr"/>
       <c r="AG25" t="b">
         <v>0</v>
       </c>
@@ -3246,42 +3242,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132710019</v>
+        <v>132709870</v>
       </c>
       <c r="B26" t="n">
-        <v>99116</v>
+        <v>57950</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3289,10 +3285,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>757281</v>
+        <v>757170</v>
       </c>
       <c r="R26" t="n">
-        <v>7175939</v>
+        <v>7175864</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3327,13 +3323,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
-      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>132709670</v>
       </c>
       <c r="B28" t="n">
-        <v>99116</v>
+        <v>99117</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132709941</v>
+        <v>132709927</v>
       </c>
       <c r="B29" t="n">
-        <v>91908</v>
+        <v>79327</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,27 +3574,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>757173</v>
+        <v>757148</v>
       </c>
       <c r="R29" t="n">
-        <v>7175914</v>
+        <v>7175922</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132709927</v>
+        <v>132708855</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>757148</v>
+        <v>757076</v>
       </c>
       <c r="R30" t="n">
-        <v>7175922</v>
+        <v>7175730</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132708855</v>
+        <v>132709519</v>
       </c>
       <c r="B31" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>757076</v>
+        <v>757001</v>
       </c>
       <c r="R31" t="n">
-        <v>7175730</v>
+        <v>7175733</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132709519</v>
+        <v>132709623</v>
       </c>
       <c r="B32" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,21 +3889,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>757001</v>
+        <v>757014</v>
       </c>
       <c r="R32" t="n">
-        <v>7175733</v>
+        <v>7175761</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,6 +3956,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>rik förekomst!</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3983,10 +3988,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132709623</v>
+        <v>132709941</v>
       </c>
       <c r="B33" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3994,27 +3999,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -4025,10 +4030,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>757014</v>
+        <v>757173</v>
       </c>
       <c r="R33" t="n">
-        <v>7175761</v>
+        <v>7175914</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4061,11 +4066,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>rik förekomst!</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4417,10 +4417,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132709906</v>
+        <v>132709425</v>
       </c>
       <c r="B37" t="n">
-        <v>57953</v>
+        <v>79327</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4428,31 +4428,30 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4460,10 +4459,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>757157</v>
+        <v>757039</v>
       </c>
       <c r="R37" t="n">
-        <v>7175889</v>
+        <v>7175739</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4498,17 +4497,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
       <c r="AE37" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF37" t="inlineStr"/>
       <c r="AG37" t="b">
         <v>0</v>
       </c>
@@ -4527,10 +4522,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132709425</v>
+        <v>132709906</v>
       </c>
       <c r="B38" t="n">
-        <v>79327</v>
+        <v>57953</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4538,30 +4533,31 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4569,10 +4565,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>757039</v>
+        <v>757157</v>
       </c>
       <c r="R38" t="n">
-        <v>7175739</v>
+        <v>7175889</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4607,13 +4603,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF38" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 63685-2025 artfynd.xlsx
+++ b/artfynd/A 63685-2025 artfynd.xlsx
@@ -779,7 +779,7 @@
         <v>132694391</v>
       </c>
       <c r="B3" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1848,32 +1848,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132710001</v>
+        <v>132709549</v>
       </c>
       <c r="B13" t="n">
-        <v>91872</v>
+        <v>91909</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1890,10 +1890,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>757256</v>
+        <v>756997</v>
       </c>
       <c r="R13" t="n">
-        <v>7175937</v>
+        <v>7175735</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,32 +1953,32 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132709549</v>
+        <v>132710001</v>
       </c>
       <c r="B14" t="n">
-        <v>91909</v>
+        <v>91872</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>5447</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1995,10 +1995,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>756997</v>
+        <v>757256</v>
       </c>
       <c r="R14" t="n">
-        <v>7175735</v>
+        <v>7175937</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2061,7 +2061,7 @@
         <v>132709496</v>
       </c>
       <c r="B15" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -3029,41 +3029,40 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132709987</v>
+        <v>132709870</v>
       </c>
       <c r="B24" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr"/>
       <c r="M24" t="inlineStr">
         <is>
-          <t>färska gnagspår</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="N24" t="inlineStr"/>
@@ -3073,10 +3072,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>757221</v>
+        <v>757170</v>
       </c>
       <c r="R24" t="n">
-        <v>7175915</v>
+        <v>7175864</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3111,13 +3110,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
-      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
@@ -3136,42 +3139,43 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132710019</v>
+        <v>132709987</v>
       </c>
       <c r="B25" t="n">
-        <v>99117</v>
+        <v>5179</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>100526</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="J25" t="inlineStr"/>
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3179,10 +3183,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>757281</v>
+        <v>757221</v>
       </c>
       <c r="R25" t="n">
-        <v>7175939</v>
+        <v>7175915</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3242,42 +3246,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132709870</v>
+        <v>132710019</v>
       </c>
       <c r="B26" t="n">
-        <v>57950</v>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3285,10 +3289,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>757170</v>
+        <v>757281</v>
       </c>
       <c r="R26" t="n">
-        <v>7175864</v>
+        <v>7175939</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3323,17 +3327,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>hål hackat i gran</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
       <c r="AE26" t="b">
         <v>0</v>
       </c>
+      <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="b">
         <v>0</v>
       </c>
@@ -3460,7 +3460,7 @@
         <v>132709670</v>
       </c>
       <c r="B28" t="n">
-        <v>99117</v>
+        <v>99118</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3563,10 +3563,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132709927</v>
+        <v>132709941</v>
       </c>
       <c r="B29" t="n">
-        <v>79327</v>
+        <v>91909</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3574,27 +3574,27 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K29" t="inlineStr"/>
@@ -3605,10 +3605,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>757148</v>
+        <v>757173</v>
       </c>
       <c r="R29" t="n">
-        <v>7175922</v>
+        <v>7175914</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3668,7 +3668,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132708855</v>
+        <v>132709927</v>
       </c>
       <c r="B30" t="n">
         <v>79327</v>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>757076</v>
+        <v>757148</v>
       </c>
       <c r="R30" t="n">
-        <v>7175730</v>
+        <v>7175922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,10 +3773,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132709519</v>
+        <v>132708855</v>
       </c>
       <c r="B31" t="n">
-        <v>80432</v>
+        <v>79327</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,21 +3784,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>757001</v>
+        <v>757076</v>
       </c>
       <c r="R31" t="n">
-        <v>7175733</v>
+        <v>7175730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132709623</v>
+        <v>132709519</v>
       </c>
       <c r="B32" t="n">
-        <v>79327</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,21 +3889,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>757014</v>
+        <v>757001</v>
       </c>
       <c r="R32" t="n">
-        <v>7175761</v>
+        <v>7175733</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3956,11 +3956,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2026-04-22</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>rik förekomst!</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3988,10 +3983,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132709941</v>
+        <v>132709623</v>
       </c>
       <c r="B33" t="n">
-        <v>91909</v>
+        <v>79327</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3999,27 +3994,27 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K33" t="inlineStr"/>
@@ -4030,10 +4025,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>757173</v>
+        <v>757014</v>
       </c>
       <c r="R33" t="n">
-        <v>7175914</v>
+        <v>7175761</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4066,6 +4061,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>rik förekomst!</t>
         </is>
       </c>
       <c r="AD33" t="b">

--- a/artfynd/A 63685-2025 artfynd.xlsx
+++ b/artfynd/A 63685-2025 artfynd.xlsx
@@ -2164,32 +2164,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132709455</v>
+        <v>132709437</v>
       </c>
       <c r="B16" t="n">
-        <v>80467</v>
+        <v>79333</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2206,10 +2206,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>757005</v>
+        <v>757012</v>
       </c>
       <c r="R16" t="n">
-        <v>7175716</v>
+        <v>7175727</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2269,42 +2269,41 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132709608</v>
+        <v>132709455</v>
       </c>
       <c r="B17" t="n">
-        <v>57958</v>
+        <v>80467</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6462</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
@@ -2312,10 +2311,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>757019</v>
+        <v>757005</v>
       </c>
       <c r="R17" t="n">
-        <v>7175747</v>
+        <v>7175716</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2350,17 +2349,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
@@ -2379,7 +2374,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132709437</v>
+        <v>132709325</v>
       </c>
       <c r="B18" t="n">
         <v>79333</v>
@@ -2408,12 +2403,12 @@
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2421,10 +2416,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>757012</v>
+        <v>757037</v>
       </c>
       <c r="R18" t="n">
-        <v>7175727</v>
+        <v>7175709</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2457,6 +2452,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132709325</v>
+        <v>132709608</v>
       </c>
       <c r="B19" t="n">
-        <v>79333</v>
+        <v>57958</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2495,28 +2495,29 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N19" t="inlineStr"/>
@@ -2526,10 +2527,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>757037</v>
+        <v>757019</v>
       </c>
       <c r="R19" t="n">
-        <v>7175709</v>
+        <v>7175747</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2566,16 +2567,15 @@
       </c>
       <c r="AC19" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>barksprätt på gran</t>
         </is>
       </c>
       <c r="AD19" t="b">
         <v>0</v>
       </c>
       <c r="AE19" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF19" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG19" t="b">
         <v>0</v>
       </c>
@@ -3668,10 +3668,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132709519</v>
+        <v>132709927</v>
       </c>
       <c r="B30" t="n">
-        <v>80438</v>
+        <v>79333</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,21 +3679,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3710,10 +3710,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>757001</v>
+        <v>757148</v>
       </c>
       <c r="R30" t="n">
-        <v>7175733</v>
+        <v>7175922</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3773,7 +3773,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132709927</v>
+        <v>132708855</v>
       </c>
       <c r="B31" t="n">
         <v>79333</v>
@@ -3815,10 +3815,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>757148</v>
+        <v>757076</v>
       </c>
       <c r="R31" t="n">
-        <v>7175922</v>
+        <v>7175730</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3878,10 +3878,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132708855</v>
+        <v>132709519</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>80438</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3889,21 +3889,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3920,10 +3920,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>757076</v>
+        <v>757001</v>
       </c>
       <c r="R32" t="n">
-        <v>7175730</v>
+        <v>7175733</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>

--- a/artfynd/A 63685-2025 artfynd.xlsx
+++ b/artfynd/A 63685-2025 artfynd.xlsx
@@ -675,36 +675,40 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>132695303</v>
+        <v>132709549</v>
       </c>
       <c r="B2" t="n">
-        <v>91881</v>
+        <v>91974</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
@@ -713,13 +717,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>757257</v>
+        <v>756997</v>
       </c>
       <c r="R2" t="n">
-        <v>7175942</v>
+        <v>7175735</v>
       </c>
       <c r="S2" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -764,22 +768,22 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>132694391</v>
+        <v>132694004</v>
       </c>
       <c r="B3" t="n">
-        <v>99130</v>
+        <v>79373</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -787,27 +791,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
@@ -815,10 +818,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>757126</v>
+        <v>757083</v>
       </c>
       <c r="R3" t="n">
-        <v>7175785</v>
+        <v>7175708</v>
       </c>
       <c r="S3" t="n">
         <v>5</v>
@@ -878,44 +881,39 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>132694155</v>
+        <v>132694051</v>
       </c>
       <c r="B4" t="n">
-        <v>58119</v>
+        <v>79373</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>
@@ -925,10 +923,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>757111</v>
+        <v>757088</v>
       </c>
       <c r="R4" t="n">
-        <v>7175854</v>
+        <v>7175752</v>
       </c>
       <c r="S4" t="n">
         <v>5</v>
@@ -969,6 +967,7 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
+      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -987,42 +986,41 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>132695248</v>
+        <v>132708855</v>
       </c>
       <c r="B5" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
@@ -1030,13 +1028,13 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>757256</v>
+        <v>757076</v>
       </c>
       <c r="R5" t="n">
-        <v>7175918</v>
+        <v>7175730</v>
       </c>
       <c r="S5" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1068,69 +1066,64 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Barksprätt tretå</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>132695144</v>
+        <v>132709325</v>
       </c>
       <c r="B6" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N6" t="inlineStr"/>
@@ -1140,13 +1133,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>757130</v>
+        <v>757037</v>
       </c>
       <c r="R6" t="n">
-        <v>7175755</v>
+        <v>7175709</v>
       </c>
       <c r="S6" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1180,7 +1173,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Barksprätt på gran</t>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1189,60 +1182,60 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
+      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>132695219</v>
+        <v>132709425</v>
       </c>
       <c r="B7" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
@@ -1250,13 +1243,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>757221</v>
+        <v>757039</v>
       </c>
       <c r="R7" t="n">
-        <v>7175916</v>
+        <v>7175739</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1288,43 +1281,39 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
+      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>132694004</v>
+        <v>132709437</v>
       </c>
       <c r="B8" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1346,7 +1335,11 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
@@ -1355,13 +1348,13 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>757083</v>
+        <v>757012</v>
       </c>
       <c r="R8" t="n">
-        <v>7175708</v>
+        <v>7175727</v>
       </c>
       <c r="S8" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1406,26 +1399,26 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>132694051</v>
+        <v>132709599</v>
       </c>
       <c r="B9" t="n">
-        <v>79333</v>
+        <v>79373</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1447,7 +1440,11 @@
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K9" t="inlineStr">
         <is>
           <t>med apothecier</t>
@@ -1460,13 +1457,13 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>757088</v>
+        <v>757009</v>
       </c>
       <c r="R9" t="n">
-        <v>7175752</v>
+        <v>7175741</v>
       </c>
       <c r="S9" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1496,6 +1493,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2026-04-22</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>fertil garnlav</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1511,54 +1513,53 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>132695275</v>
+        <v>132709623</v>
       </c>
       <c r="B10" t="n">
-        <v>57958</v>
+        <v>79373</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1566,13 +1567,13 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>757254</v>
+        <v>757014</v>
       </c>
       <c r="R10" t="n">
-        <v>7175939</v>
+        <v>7175761</v>
       </c>
       <c r="S10" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1606,7 +1607,7 @@
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>Barksprätt på gran</t>
+          <t>rik förekomst!</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1615,60 +1616,60 @@
       <c r="AE10" t="b">
         <v>0</v>
       </c>
+      <c r="AF10" t="inlineStr"/>
       <c r="AG10" t="b">
         <v>0</v>
       </c>
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>132695182</v>
+        <v>132708867</v>
       </c>
       <c r="B11" t="n">
-        <v>57958</v>
+        <v>80382</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100109</v>
+        <v>6456</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skinnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Leptogium saturninum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Dicks.) Nyl.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr"/>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
@@ -1676,13 +1677,13 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>757082</v>
+        <v>757057</v>
       </c>
       <c r="R11" t="n">
-        <v>7175763</v>
+        <v>7175737</v>
       </c>
       <c r="S11" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1720,28 +1721,29 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
+      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>132694107</v>
+        <v>132709451</v>
       </c>
       <c r="B12" t="n">
-        <v>57958</v>
+        <v>80488</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1749,31 +1751,30 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
@@ -1781,13 +1782,13 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>757052</v>
+        <v>757005</v>
       </c>
       <c r="R12" t="n">
-        <v>7175765</v>
+        <v>7175716</v>
       </c>
       <c r="S12" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1819,67 +1820,63 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>Barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
       <c r="AE12" t="b">
         <v>0</v>
       </c>
+      <c r="AF12" t="inlineStr"/>
       <c r="AG12" t="b">
         <v>0</v>
       </c>
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Tommy Boström</t>
+          <t>Patrik Nygren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>132710001</v>
+        <v>132709519</v>
       </c>
       <c r="B13" t="n">
-        <v>91881</v>
+        <v>80488</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K13" t="inlineStr"/>
@@ -1890,10 +1887,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>757256</v>
+        <v>757001</v>
       </c>
       <c r="R13" t="n">
-        <v>7175937</v>
+        <v>7175733</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1953,38 +1950,38 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>132709549</v>
+        <v>132709455</v>
       </c>
       <c r="B14" t="n">
-        <v>91918</v>
+        <v>80493</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>1202</v>
+        <v>6462</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
-          <t>fruktkroppar</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K14" t="inlineStr"/>
@@ -1995,10 +1992,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>756997</v>
+        <v>757005</v>
       </c>
       <c r="R14" t="n">
-        <v>7175735</v>
+        <v>7175716</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2058,42 +2055,42 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>132709496</v>
+        <v>132709430</v>
       </c>
       <c r="B15" t="n">
-        <v>99130</v>
+        <v>57972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
@@ -2101,10 +2098,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>756999</v>
+        <v>757039</v>
       </c>
       <c r="R15" t="n">
-        <v>7175722</v>
+        <v>7175739</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2139,13 +2136,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>äldre hack i basen på en jättegran</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
       <c r="AE15" t="b">
         <v>0</v>
       </c>
-      <c r="AF15" t="inlineStr"/>
       <c r="AG15" t="b">
         <v>0</v>
       </c>
@@ -2164,10 +2165,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>132709437</v>
+        <v>132694107</v>
       </c>
       <c r="B16" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2175,30 +2176,31 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
@@ -2206,13 +2208,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>757012</v>
+        <v>757052</v>
       </c>
       <c r="R16" t="n">
-        <v>7175727</v>
+        <v>7175765</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2244,35 +2246,39 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD16" t="b">
         <v>0</v>
       </c>
       <c r="AE16" t="b">
         <v>0</v>
       </c>
-      <c r="AF16" t="inlineStr"/>
       <c r="AG16" t="b">
         <v>0</v>
       </c>
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>132709325</v>
+        <v>132695182</v>
       </c>
       <c r="B17" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2280,28 +2286,29 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N17" t="inlineStr"/>
@@ -2311,13 +2318,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>757037</v>
+        <v>757082</v>
       </c>
       <c r="R17" t="n">
-        <v>7175709</v>
+        <v>7175763</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2349,71 +2356,66 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>fertil garnlav</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
-      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>132709455</v>
+        <v>132709608</v>
       </c>
       <c r="B18" t="n">
-        <v>80467</v>
+        <v>57975</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
@@ -2421,10 +2423,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>757005</v>
+        <v>757019</v>
       </c>
       <c r="R18" t="n">
-        <v>7175716</v>
+        <v>7175747</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2459,13 +2461,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD18" t="b">
         <v>0</v>
       </c>
       <c r="AE18" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF18" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG18" t="b">
         <v>0</v>
       </c>
@@ -2484,10 +2490,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>132709608</v>
+        <v>132709648</v>
       </c>
       <c r="B19" t="n">
-        <v>57958</v>
+        <v>57975</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2527,10 +2533,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>757019</v>
+        <v>757096</v>
       </c>
       <c r="R19" t="n">
-        <v>7175747</v>
+        <v>7175748</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2594,10 +2600,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>132709716</v>
+        <v>132694155</v>
       </c>
       <c r="B20" t="n">
-        <v>57958</v>
+        <v>58136</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2605,29 +2611,33 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr"/>
       <c r="M20" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>par i lämplig häckbiotop</t>
         </is>
       </c>
       <c r="N20" t="inlineStr"/>
@@ -2637,13 +2647,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>757180</v>
+        <v>757111</v>
       </c>
       <c r="R20" t="n">
-        <v>7175845</v>
+        <v>7175854</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2675,16 +2685,11 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
       <c r="AE20" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG20" t="b">
         <v>0</v>
@@ -2692,54 +2697,54 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>132709430</v>
+        <v>132709496</v>
       </c>
       <c r="B21" t="n">
-        <v>57955</v>
+        <v>99195</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
@@ -2747,10 +2752,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>757039</v>
+        <v>756999</v>
       </c>
       <c r="R21" t="n">
-        <v>7175739</v>
+        <v>7175722</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2785,17 +2790,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>äldre hack i basen på en jättegran</t>
-        </is>
-      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
       <c r="AE21" t="b">
         <v>0</v>
       </c>
+      <c r="AF21" t="inlineStr"/>
       <c r="AG21" t="b">
         <v>0</v>
       </c>
@@ -2814,41 +2815,42 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>132709778</v>
+        <v>132709670</v>
       </c>
       <c r="B22" t="n">
-        <v>80467</v>
+        <v>99195</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
-          <t>bålar</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr"/>
       <c r="N22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
@@ -2856,10 +2858,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>757164</v>
+        <v>757108</v>
       </c>
       <c r="R22" t="n">
-        <v>7175781</v>
+        <v>7175764</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2919,10 +2921,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>132709648</v>
+        <v>132709941</v>
       </c>
       <c r="B23" t="n">
-        <v>57958</v>
+        <v>91974</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2930,31 +2932,30 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
@@ -2962,10 +2963,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>757096</v>
+        <v>757173</v>
       </c>
       <c r="R23" t="n">
-        <v>7175748</v>
+        <v>7175914</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3000,17 +3001,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD23" t="b">
         <v>0</v>
       </c>
       <c r="AE23" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF23" t="inlineStr"/>
       <c r="AG23" t="b">
         <v>0</v>
       </c>
@@ -3029,42 +3026,37 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>132709870</v>
+        <v>132695303</v>
       </c>
       <c r="B24" t="n">
-        <v>57955</v>
+        <v>91937</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>100049</v>
+        <v>5447</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
       <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
@@ -3072,13 +3064,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>757170</v>
+        <v>757257</v>
       </c>
       <c r="R24" t="n">
-        <v>7175864</v>
+        <v>7175942</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3110,71 +3102,66 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>hål hackat i gran</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
       <c r="AE24" t="b">
         <v>0</v>
       </c>
+      <c r="AF24" t="inlineStr"/>
       <c r="AG24" t="b">
         <v>0</v>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>132710019</v>
+        <v>132710001</v>
       </c>
       <c r="B25" t="n">
-        <v>99130</v>
+        <v>91937</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>fruktkroppar</t>
         </is>
       </c>
       <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
@@ -3182,10 +3169,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>757281</v>
+        <v>757256</v>
       </c>
       <c r="R25" t="n">
-        <v>7175939</v>
+        <v>7175937</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3245,43 +3232,41 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>132709987</v>
+        <v>132709927</v>
       </c>
       <c r="B26" t="n">
-        <v>5179</v>
+        <v>79373</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>bålar</t>
+        </is>
+      </c>
       <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr"/>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>färska gnagspår</t>
-        </is>
-      </c>
       <c r="N26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
@@ -3289,10 +3274,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>757221</v>
+        <v>757148</v>
       </c>
       <c r="R26" t="n">
-        <v>7175915</v>
+        <v>7175922</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3352,10 +3337,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>132709773</v>
+        <v>132709778</v>
       </c>
       <c r="B27" t="n">
-        <v>80473</v>
+        <v>80493</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3363,21 +3348,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6463</v>
+        <v>6462</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3457,42 +3442,41 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>132709670</v>
+        <v>132709773</v>
       </c>
       <c r="B28" t="n">
-        <v>99130</v>
+        <v>80499</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>bålar</t>
         </is>
       </c>
       <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
@@ -3500,10 +3484,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>757108</v>
+        <v>757164</v>
       </c>
       <c r="R28" t="n">
-        <v>7175764</v>
+        <v>7175781</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3563,41 +3547,42 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>132709927</v>
+        <v>132709870</v>
       </c>
       <c r="B29" t="n">
-        <v>79333</v>
+        <v>57972</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr"/>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
@@ -3605,10 +3590,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>757148</v>
+        <v>757170</v>
       </c>
       <c r="R29" t="n">
-        <v>7175922</v>
+        <v>7175864</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3643,13 +3628,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>hål hackat i gran</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
       <c r="AE29" t="b">
         <v>0</v>
       </c>
-      <c r="AF29" t="inlineStr"/>
       <c r="AG29" t="b">
         <v>0</v>
       </c>
@@ -3668,10 +3657,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>132708855</v>
+        <v>132695144</v>
       </c>
       <c r="B30" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3679,30 +3668,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr"/>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
@@ -3710,13 +3700,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>757076</v>
+        <v>757130</v>
       </c>
       <c r="R30" t="n">
-        <v>7175730</v>
+        <v>7175755</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3748,35 +3738,39 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
       <c r="AE30" t="b">
         <v>0</v>
       </c>
-      <c r="AF30" t="inlineStr"/>
       <c r="AG30" t="b">
         <v>0</v>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>132709623</v>
+        <v>132695219</v>
       </c>
       <c r="B31" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3784,30 +3778,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr"/>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
@@ -3815,13 +3810,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>757014</v>
+        <v>757221</v>
       </c>
       <c r="R31" t="n">
-        <v>7175761</v>
+        <v>7175916</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3855,7 +3850,7 @@
       </c>
       <c r="AC31" t="inlineStr">
         <is>
-          <t>rik förekomst!</t>
+          <t>Barksprätt på gran</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3864,29 +3859,28 @@
       <c r="AE31" t="b">
         <v>0</v>
       </c>
-      <c r="AF31" t="inlineStr"/>
       <c r="AG31" t="b">
         <v>0</v>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>132709599</v>
+        <v>132695248</v>
       </c>
       <c r="B32" t="n">
-        <v>79333</v>
+        <v>57975</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3894,32 +3888,29 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr"/>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="N32" t="inlineStr"/>
@@ -3929,13 +3920,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>757009</v>
+        <v>757256</v>
       </c>
       <c r="R32" t="n">
-        <v>7175741</v>
+        <v>7175918</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3969,7 +3960,7 @@
       </c>
       <c r="AC32" t="inlineStr">
         <is>
-          <t>fertil garnlav</t>
+          <t>Barksprätt tretå</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3978,29 +3969,28 @@
       <c r="AE32" t="b">
         <v>0</v>
       </c>
-      <c r="AF32" t="inlineStr"/>
       <c r="AG32" t="b">
         <v>0</v>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>132709519</v>
+        <v>132695275</v>
       </c>
       <c r="B33" t="n">
-        <v>80438</v>
+        <v>57975</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4008,30 +3998,31 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr"/>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
@@ -4039,13 +4030,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>757001</v>
+        <v>757254</v>
       </c>
       <c r="R33" t="n">
-        <v>7175733</v>
+        <v>7175939</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4077,35 +4068,39 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD33" t="b">
         <v>0</v>
       </c>
       <c r="AE33" t="b">
         <v>0</v>
       </c>
-      <c r="AF33" t="inlineStr"/>
       <c r="AG33" t="b">
         <v>0</v>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>132709941</v>
+        <v>132709716</v>
       </c>
       <c r="B34" t="n">
-        <v>91918</v>
+        <v>57975</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4113,30 +4108,31 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
       <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr"/>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
@@ -4144,10 +4140,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>757173</v>
+        <v>757180</v>
       </c>
       <c r="R34" t="n">
-        <v>7175914</v>
+        <v>7175845</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4182,13 +4178,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
       <c r="AE34" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF34" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG34" t="b">
         <v>0</v>
       </c>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>132709451</v>
+        <v>132709906</v>
       </c>
       <c r="B35" t="n">
-        <v>80438</v>
+        <v>57975</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4218,30 +4218,31 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
       <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="N35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
@@ -4249,10 +4250,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>757005</v>
+        <v>757157</v>
       </c>
       <c r="R35" t="n">
-        <v>7175716</v>
+        <v>7175889</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4287,13 +4288,17 @@
           <t>2026-04-22</t>
         </is>
       </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>barksprätt på gran</t>
+        </is>
+      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
       <c r="AE35" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF35" t="inlineStr"/>
+        <v>1</v>
+      </c>
       <c r="AG35" t="b">
         <v>0</v>
       </c>
@@ -4312,10 +4317,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>132708867</v>
+        <v>132709987</v>
       </c>
       <c r="B36" t="n">
-        <v>80342</v>
+        <v>5181</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4323,30 +4328,32 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6456</v>
+        <v>100526</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Skinnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Leptogium saturninum</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Dicks.) Nyl.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J36" t="inlineStr"/>
       <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr"/>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>färska gnagspår</t>
+        </is>
+      </c>
       <c r="N36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
@@ -4354,10 +4361,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>757057</v>
+        <v>757221</v>
       </c>
       <c r="R36" t="n">
-        <v>7175737</v>
+        <v>7175915</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4417,41 +4424,38 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>132709425</v>
+        <v>132694391</v>
       </c>
       <c r="B37" t="n">
-        <v>79333</v>
+        <v>99195</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>bålar</t>
-        </is>
-      </c>
+      <c r="J37" t="inlineStr"/>
       <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
@@ -4459,13 +4463,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>757039</v>
+        <v>757126</v>
       </c>
       <c r="R37" t="n">
-        <v>7175739</v>
+        <v>7175785</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4510,54 +4514,54 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Patrik Nygren</t>
+          <t>Tommy Boström</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>132709906</v>
+        <v>132710019</v>
       </c>
       <c r="B38" t="n">
-        <v>57958</v>
+        <v>99195</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="N38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
@@ -4565,10 +4569,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>757157</v>
+        <v>757281</v>
       </c>
       <c r="R38" t="n">
-        <v>7175889</v>
+        <v>7175939</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4603,17 +4607,13 @@
           <t>2026-04-22</t>
         </is>
       </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>barksprätt på gran</t>
-        </is>
-      </c>
       <c r="AD38" t="b">
         <v>0</v>
       </c>
       <c r="AE38" t="b">
-        <v>1</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AF38" t="inlineStr"/>
       <c r="AG38" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 63685-2025 artfynd.xlsx
+++ b/artfynd/A 63685-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY38"/>
+  <dimension ref="A1:AZ38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -777,6 +782,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709549</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -882,6 +892,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709941</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -983,6 +998,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695303</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1088,6 +1108,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710001</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1189,6 +1214,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132694004</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1294,6 +1324,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132694051</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1399,6 +1434,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708855</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1509,6 +1549,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709325</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1614,6 +1659,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709425</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1719,6 +1769,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709437</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1833,6 +1888,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709599</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1943,6 +2003,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709623</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2048,6 +2113,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709927</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2153,6 +2223,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132708867</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2258,6 +2333,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709451</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2363,6 +2443,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709519</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2468,6 +2553,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709455</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2573,6 +2663,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709778</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2678,6 +2773,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709773</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2788,6 +2888,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709430</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2898,6 +3003,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709870</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3008,6 +3118,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132694107</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3118,6 +3233,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695144</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3223,6 +3343,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695182</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3333,6 +3458,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695219</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3443,6 +3573,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695248</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3553,6 +3688,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132695275</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3663,6 +3803,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709608</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3773,6 +3918,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709648</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3883,6 +4033,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709716</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3993,6 +4148,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709906</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4100,6 +4260,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709987</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4209,6 +4374,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132694155</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4311,6 +4481,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132694391</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4417,6 +4592,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709496</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4523,6 +4703,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132709670</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4629,8 +4814,52 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/132710019</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>